--- a/results/by_outcome/full_results_education_PGI_Brothers_MI.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Brothers_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5914681827557</v>
+        <v>0.587058444566714</v>
       </c>
       <c r="I2" t="n">
-        <v>0.293511833489044</v>
+        <v>0.291280893629695</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.408801854619293</v>
+        <v>0.413209944631803</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.581037529563094</v>
+        <v>0.579754925296008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.315587189877515</v>
+        <v>0.316208767779243</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.604931489434978</v>
+        <v>0.604494668942537</v>
       </c>
       <c r="D4" t="n">
-        <v>0.39552527286429</v>
+        <v>0.395962722566054</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00045676229927</v>
+        <v>1.00045739150859</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.395344694061389</v>
+        <v>0.39578168967042</v>
       </c>
       <c r="K4" t="n">
-        <v>0.315443107225856</v>
+        <v>0.316064197879014</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0104258905259638</v>
+        <v>-0.00730017889478239</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0134571605579048</v>
+        <v>0.017428254961383</v>
       </c>
       <c r="N4" t="n">
-        <v>0.305017216699892</v>
+        <v>0.308764018984231</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.395344694061389</v>
+        <v>0.39578168967042</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3303242526774</v>
+        <v>0.328594216081977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.460365135445377</v>
+        <v>0.462969163258863</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00000000000000000000000000000000962990247472261</v>
+        <v>0.000000000000000000000000000000781104589457592</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.305017216699892</v>
+        <v>0.308764018984231</v>
       </c>
       <c r="D3" t="n">
-        <v>0.234807475418613</v>
+        <v>0.241984852728234</v>
       </c>
       <c r="E3" t="n">
-        <v>0.375226957981171</v>
+        <v>0.375543185240228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0000000000000000168154307612359</v>
+        <v>0.000000000000000000131648807775</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.408801854619293</v>
+        <v>0.413209944631803</v>
       </c>
       <c r="D4" t="n">
-        <v>0.338371239199597</v>
+        <v>0.34682458405718</v>
       </c>
       <c r="E4" t="n">
-        <v>0.47923247003899</v>
+        <v>0.479595305206427</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00000000000000000000000000000563692341383659</v>
+        <v>0.000000000000000000000000000000000342491941276953</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.103784637919402</v>
+        <v>0.104445925647572</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0660163307293386</v>
+        <v>0.0709503794170452</v>
       </c>
       <c r="E5" t="n">
-        <v>0.141552945109465</v>
+        <v>0.137941471878099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0000000721068200561201</v>
+        <v>0.000000000986591587381948</v>
       </c>
     </row>
   </sheetData>
